--- a/tests/realSuite/Piano-Viaggi_Palla-Tamburello_22-aprile-2026/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Palla-Tamburello_22-aprile-2026/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC CLES</t>
+          <t>IC ALTA VALLAGARINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Piazza Fiera - Cles</t>
+          <t>Da definire - Calliano</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC DRO</t>
+          <t>IC ALTA VALLAGARINA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Via S. Antonio 17 - Dro</t>
+          <t>Da definire - Volano</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC FOLGARIA LAVARONE</t>
+          <t>IC CLES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Frazione Gionghi - Lavarone</t>
+          <t>Piazza Fiera - Cles</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -511,12 +511,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC FONDO</t>
+          <t>IC DRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Via Canestrini - Revò</t>
+          <t>Via S. Antonio 17 - Dro</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -526,87 +526,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC ISERA - ROVERETO</t>
+          <t>IC FOLGARIA LAVARONE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viale della Vittoria, 43 - Rovereto</t>
+          <t>Fermata Bus - Mezzamonte</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC MEZZOCORONA</t>
+          <t>IC FOLGARIA LAVARONE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Via Fornai 1 - Mezzocorona</t>
+          <t>Frazione Gionghi - Lavarone</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC FOLGARIA LAVARONE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Via degli Alpini 17 - Mezzolombardo</t>
+          <t>Park Palaghiaccio - Folgaria</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC RIVA 1</t>
+          <t>IC FONDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viale Damiano Chiesa, 10 – Riva del Garda</t>
+          <t>Via Canestrini - Revò</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC ISERA - ROVERETO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Via Circonvalazione 44 - Tione</t>
+          <t>Viale della Vittoria, 43 - Rovereto</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC TRENTO 1</t>
+          <t>IC MEZZOCORONA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Via Znojmo 24 – Povo - Trento</t>
+          <t>Via Fornai 1 - Mezzocorona</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -616,75 +616,135 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Piazza Palù, Madonna di Campiglio</t>
+          <t>Via degli Alpini 17 - Mezzolombardo</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC VALLE DEI LAGHI</t>
+          <t>IC RIVA 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Via Roma 3 - Vezzano</t>
+          <t>Viale Damiano Chiesa, 10 – Riva del Garda</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC VALLE DEI LAGHI</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Via XXV Aprile 7 - Cavedine</t>
+          <t>Via Circonvalazione 44 - Tione</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC VILLA LAGARINA</t>
+          <t>IC TRENTO 1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Via Stockstadt Am Rhein, 3 – Villa Lagarina</t>
+          <t>Via Znojmo 24 – Povo - Trento</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>IC VAL RENDENA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Piazza Palù, Madonna di Campiglio</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IC VALLE DEI LAGHI</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Via Roma 3 - Vezzano</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IC VALLE DEI LAGHI</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Via XXV Aprile 7 - Cavedine</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IC VILLA LAGARINA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Via Stockstadt Am Rhein, 3 – Villa Lagarina</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>IS MARTINO MARTINI – Students staff</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Via Perlasca 4 - Mezzolombardo</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C22" t="n">
         <v>20</v>
       </c>
     </row>

--- a/tests/realSuite/Piano-Viaggi_Palla-Tamburello_22-aprile-2026/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Palla-Tamburello_22-aprile-2026/input.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Via Betta 9 - Ala</t>
+          <t>Scuola primaria "Abramo Betta", 9, Via Abramo Betta, Ala, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38061, Italia</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/tests/realSuite/Piano-Viaggi_Palla-Tamburello_22-aprile-2026/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Palla-Tamburello_22-aprile-2026/input.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Da definire - Besenello</t>
+          <t>Via Alcide De Gasperi, Besenello, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38060, Italia</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -471,7 +471,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Da definire - Calliano</t>
+          <t>Via Alcide Degasperi, Calliano, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38060, Italia</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Da definire - Volano</t>
+          <t>Scuola Elementare Giangrisostomo Tovazzi, 30, Via Stazione, Volano, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38060, Italia</t>
         </is>
       </c>
       <c r="C5" t="n">
